--- a/trading_signals/risk_management/risk_workbook_20260618_043733.xlsx
+++ b/trading_signals/risk_management/risk_workbook_20260618_043733.xlsx
@@ -723,7 +723,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Signal date 2026-06-17  ·  Generated 2026-06-24T17:42:58  ·  Scope: MRPT+MTFS pairs book (model-based, broker-reconciled)</t>
+          <t>Signal date 2026-06-17  ·  Generated 2026-06-24T18:51:41  ·  Scope: MRPT+MTFS pairs book (model-based, broker-reconciled)</t>
         </is>
       </c>
     </row>
